--- a/storage/app/private/filament_exports/2/export-2-registrants.xlsx
+++ b/storage/app/private/filament_exports/2/export-2-registrants.xlsx
@@ -60,7 +60,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F58"/>
   <sheetData>
     <row r="1" spans="1:6" customHeight="0">
       <c r="A1" s="0" t="inlineStr">
@@ -97,1425 +97,1425 @@
     <row r="2" spans="1:6" customHeight="0">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t>Abdalaziz</t>
+          <t>Mostafa</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>El Gafy</t>
+          <t>Elhanoun</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
         <is>
-          <t>Horyah</t>
+          <t>Stada</t>
         </is>
       </c>
       <c r="D2" s="0" t="inlineStr">
         <is>
-          <t>Hdjrihr</t>
+          <t>Pharmacist </t>
         </is>
       </c>
       <c r="E2" s="0" t="inlineStr">
         <is>
-          <t>elgafy@briskera.com</t>
+          <t>mostafa.elhanoun@stada.com</t>
         </is>
       </c>
       <c r="F2" s="0" t="inlineStr">
         <is>
-          <t>01008084006</t>
+          <t>0564095010</t>
         </is>
       </c>
     </row>
     <row r="3" spans="1:6" customHeight="0">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>Mohamed</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>Taher</t>
+          <t>Morshed</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Sdi</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>Designer </t>
+          <t>IT </t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>ahmedtaher.speed@gmail.com</t>
+          <t>mohamedsaid1433@gmail.com</t>
         </is>
       </c>
       <c r="F3" s="0" t="inlineStr">
         <is>
-          <t>056200</t>
+          <t>0506021326</t>
         </is>
       </c>
     </row>
     <row r="4" spans="1:6" customHeight="0">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t>Mohammad</t>
+          <t>Hamada</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>Hammad</t>
+          <t>Eldouh</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>Cmc</t>
+          <t>R &amp; D</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>Gp</t>
+          <t>Dermocosmetic</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>al-hammad00@hotmail.com</t>
+          <t>hamada.eldouh@gmail.com</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>0508211100</t>
+          <t>+33658411024</t>
         </is>
       </c>
     </row>
     <row r="5" spans="1:6" customHeight="0">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t>Ali</t>
+          <t>Maha</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>Alhashem</t>
+          <t>Mubaidein</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>Ethrainvest</t>
+          <t>Privat</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t>Wealth relation</t>
+          <t>Medicine</t>
         </is>
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t>alhashim@ethrainvest.com</t>
+          <t>mahaissa2008@gmail.com</t>
         </is>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>0558223321</t>
+          <t>0549878708</t>
         </is>
       </c>
     </row>
     <row r="6" spans="1:6" customHeight="0">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t>Tamer</t>
+          <t>Issa</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>Elsayed</t>
+          <t>Azzam</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>Almohanna pharmacies</t>
+          <t>Faqeeh</t>
         </is>
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t>Sales manager</t>
+          <t>Dermatology</t>
         </is>
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
-          <t>elsayedtamer.pharm@gmail.com</t>
+          <t>issa65@yahoo.com</t>
         </is>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>0545968312</t>
+          <t>0549878708</t>
         </is>
       </c>
     </row>
     <row r="7" spans="1:6" customHeight="0">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t>Mostafa mohammed</t>
+          <t>Samar</t>
         </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>Elkholy</t>
+          <t>Shosha</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>Medical balsam pharmacy</t>
+          <t>Dr Suliman alhabib hospital</t>
         </is>
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t>Pharmacist</t>
+          <t>Dermatology</t>
         </is>
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
-          <t>dr_mo_ph@yahoo.com</t>
+          <t>shoshasamar4@gmail.com</t>
         </is>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>0563806877</t>
+          <t>0508971351</t>
         </is>
       </c>
     </row>
     <row r="8" spans="1:6" customHeight="0">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t>Mohamed </t>
+          <t>Reham</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>Abouelhassan</t>
+          <t>Osman</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>Medical balsam pharmacy</t>
+          <t>Smc</t>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t>Pharmacict</t>
+          <t>Dermatology </t>
         </is>
       </c>
       <c r="E8" s="0" t="inlineStr">
         <is>
-          <t>mmuhamed651@gmail.com</t>
+          <t>rehamosman18@gmail.com</t>
         </is>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>0568477366</t>
+          <t>0566052293</t>
         </is>
       </c>
     </row>
     <row r="9" spans="1:6" customHeight="0">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t>Fatimah</t>
+          <t>Basma</t>
         </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>Abduljalel</t>
+          <t>Ragab</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>Ram</t>
+          <t>Qassim national hospital</t>
         </is>
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t>Derma</t>
+          <t>Dermatology</t>
         </is>
       </c>
       <c r="E9" s="0" t="inlineStr">
         <is>
-          <t>f.almoliky84@gmail.com</t>
+          <t>basmaragab75@yahoo.com</t>
         </is>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>0508370127</t>
+          <t>0545199212</t>
         </is>
       </c>
     </row>
     <row r="10" spans="1:6" customHeight="0">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t>Heba</t>
+          <t>Thamar</t>
         </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>El Shouni</t>
+          <t>Elkhawaga</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>KGH</t>
+          <t>Infinity</t>
         </is>
       </c>
       <c r="D10" s="0" t="inlineStr">
         <is>
-          <t>Ophthalmology</t>
+          <t>Dermatology </t>
         </is>
       </c>
       <c r="E10" s="0" t="inlineStr">
         <is>
-          <t>dr_heba@hotmail.com</t>
+          <t>elthamar1871985@gmail.com</t>
         </is>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>0540403001</t>
+          <t>0533584815</t>
         </is>
       </c>
     </row>
     <row r="11" spans="1:6" customHeight="0">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t>Adel</t>
+          <t>Mohamed</t>
         </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>Reslan</t>
+          <t>Eleraqy</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>Almana medical centre  raka </t>
+          <t>smch </t>
         </is>
       </c>
       <c r="D11" s="0" t="inlineStr">
         <is>
-          <t>Dermatologist </t>
+          <t>Dermatology </t>
         </is>
       </c>
       <c r="E11" s="0" t="inlineStr">
         <is>
-          <t>adel.reslan@gmail.com</t>
+          <t>sphinxegypty@yahoo.com</t>
         </is>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>0569363102</t>
+          <t>0540052851</t>
         </is>
       </c>
     </row>
     <row r="12" spans="1:6" customHeight="0">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t>Ahmed </t>
+          <t>Asma</t>
         </is>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>Hammad</t>
+          <t>Sikander</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>Alhabib</t>
+          <t>Medical world polyclinic</t>
         </is>
       </c>
       <c r="D12" s="0" t="inlineStr">
         <is>
-          <t>Dermatologist </t>
+          <t>General physician</t>
         </is>
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
-          <t>a_s_hammad@hotmail.com</t>
+          <t>asmafree67@yahoo.com</t>
         </is>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>0547792080</t>
+          <t>0501779421</t>
         </is>
       </c>
     </row>
     <row r="13" spans="1:6" customHeight="0">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t>Mahmoud </t>
+          <t>Mohammed</t>
         </is>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>Ashry</t>
+          <t>Alraddadi</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>Exceer comp</t>
+          <t>Hmg</t>
         </is>
       </c>
       <c r="D13" s="0" t="inlineStr">
         <is>
-          <t>Pharmacy supervisor </t>
+          <t>Dermatology</t>
         </is>
       </c>
       <c r="E13" s="0" t="inlineStr">
         <is>
-          <t>mahmoudashry28@gmail.com</t>
+          <t>dr.mo.alraddadi@gmail.com</t>
         </is>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>0545022856</t>
+          <t>0581876666</t>
         </is>
       </c>
     </row>
     <row r="14" spans="1:6" customHeight="0">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t>Lia</t>
+          <t>Amira</t>
         </is>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>Alkablan</t>
+          <t>Elboraei</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>Alhokail</t>
+          <t>Prozone</t>
         </is>
       </c>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t>Pediatrics</t>
+          <t>Dermatologist</t>
         </is>
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
-          <t>laya.kabalan@gmail.com</t>
+          <t>amira.alboraei@yahoo</t>
         </is>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>0508544795</t>
+          <t>0580160421</t>
         </is>
       </c>
     </row>
     <row r="15" spans="1:6" customHeight="0">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t>Noha</t>
+          <t>Rima</t>
         </is>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>Rifaat</t>
+          <t>Aboukheir</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>Alyousif hospital</t>
+          <t>Kingdom hospital</t>
         </is>
       </c>
       <c r="D15" s="0" t="inlineStr">
         <is>
-          <t>Dermatologist</t>
+          <t>Dermatology</t>
         </is>
       </c>
       <c r="E15" s="0" t="inlineStr">
         <is>
-          <t>noha_rif@hotmail.com</t>
+          <t>abkrima@gmail.com</t>
         </is>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>0542349107</t>
+          <t>0506192785</t>
         </is>
       </c>
     </row>
     <row r="16" spans="1:6" customHeight="0">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t>Donia</t>
+          <t>Chaima</t>
         </is>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>Rafat</t>
+          <t>Kouki</t>
         </is>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>Khalid alruhaimi clinic</t>
+          <t>Dr Sulaiman alhabib nakheel</t>
         </is>
       </c>
       <c r="D16" s="0" t="inlineStr">
         <is>
-          <t>Dermatologist </t>
+          <t>Dermatologist</t>
         </is>
       </c>
       <c r="E16" s="0" t="inlineStr">
         <is>
-          <t>doniaty2@yahoo.com</t>
+          <t>koukichaima2311@gmail.com</t>
         </is>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>0591202209</t>
+          <t>0539170806</t>
         </is>
       </c>
     </row>
     <row r="17" spans="1:6" customHeight="0">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t>Samiha</t>
+          <t>Sawsan</t>
         </is>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>Arafat</t>
+          <t>Mohamed</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>Mikyas medical complex </t>
+          <t>Dallah</t>
         </is>
       </c>
       <c r="D17" s="0" t="inlineStr">
         <is>
-          <t>Dermatologist </t>
+          <t>Derma</t>
         </is>
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
-          <t>s.arafat55@yahoo.com</t>
+          <t>sawsanothman85@yahoo.com</t>
         </is>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>0504805202</t>
+          <t>0501979967</t>
         </is>
       </c>
     </row>
     <row r="18" spans="1:6" customHeight="0">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Rania</t>
         </is>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>Albreiki</t>
+          <t>Almahrous</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>KFHU</t>
+          <t>Hmg</t>
         </is>
       </c>
       <c r="D18" s="0" t="inlineStr">
         <is>
-          <t>Dermatologist </t>
+          <t>Dermatologist</t>
         </is>
       </c>
       <c r="E18" s="0" t="inlineStr">
         <is>
-          <t>salbreiki@yahoo.com</t>
+          <t>al_mahrous64@hotmail.com</t>
         </is>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>0505879236</t>
+          <t>0557334688</t>
         </is>
       </c>
     </row>
     <row r="19" spans="1:6" customHeight="0">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t>Sameer</t>
+          <t>Samar</t>
         </is>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>Hasanen</t>
+          <t>Saeed</t>
         </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>Hoor polyclinic</t>
+          <t>Kaya rawdah</t>
         </is>
       </c>
       <c r="D19" s="0" t="inlineStr">
         <is>
-          <t>Dermatologist </t>
+          <t>Dermatology senior registrar</t>
         </is>
       </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
-          <t>samir_hassanein@yahoo.com</t>
+          <t>samarashmawy88@gmail.com</t>
         </is>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>0501943881</t>
+          <t>0508659411</t>
         </is>
       </c>
     </row>
     <row r="20" spans="1:6" customHeight="0">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t>Tarek</t>
+          <t>Basem</t>
         </is>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>Alattar</t>
+          <t>Adada</t>
         </is>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>Almana hospital.</t>
+          <t>Alzajeera hospital</t>
         </is>
       </c>
       <c r="D20" s="0" t="inlineStr">
         <is>
-          <t>Paediatrician </t>
+          <t>Dermatology </t>
         </is>
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
-          <t>tarekhatem70@yahoo.com</t>
+          <t>drbasem@gmail.com</t>
         </is>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>0561462126</t>
+          <t>0563245642</t>
         </is>
       </c>
     </row>
     <row r="21" spans="1:6" customHeight="0">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t>Ibrahim</t>
+          <t>Nezar</t>
         </is>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>Sabry</t>
+          <t>El tarras</t>
         </is>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>Adawaa</t>
+          <t>How polyclinic</t>
         </is>
       </c>
       <c r="D21" s="0" t="inlineStr">
         <is>
-          <t>Markiting</t>
+          <t>Derma</t>
         </is>
       </c>
       <c r="E21" s="0" t="inlineStr">
         <is>
-          <t>imhhema@yahoo.com</t>
+          <t>eltarrasyahya@gmail.com</t>
         </is>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>0542627486</t>
+          <t>0542725601</t>
         </is>
       </c>
     </row>
     <row r="22" spans="1:6" customHeight="0">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t>Abulrahman</t>
+          <t>Ismail</t>
         </is>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>Faraj</t>
+          <t>Gohar</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>Dawaa</t>
+          <t>Al Habib pharmacy</t>
         </is>
       </c>
       <c r="D22" s="0" t="inlineStr">
         <is>
-          <t>Pharmacist</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E22" s="0" t="inlineStr">
         <is>
-          <t>abdogamil227@gmail.com</t>
+          <t>goharsoma@gmail.com</t>
         </is>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>0548890871</t>
+          <t>0535146277</t>
         </is>
       </c>
     </row>
     <row r="23" spans="1:6" customHeight="0">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t>Mohamed </t>
+          <t>Mohamed</t>
         </is>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>Elsayrfy</t>
+          <t>Ramzy</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>Almana medical center alrakah</t>
+          <t>Soliman elhabib</t>
         </is>
       </c>
       <c r="D23" s="0" t="inlineStr">
         <is>
-          <t>Pediatrics</t>
+          <t>Doctor</t>
         </is>
       </c>
       <c r="E23" s="0" t="inlineStr">
         <is>
-          <t>emohamedmortada@hotmail.com</t>
+          <t>mohamed.ramsy7272@gmail.com</t>
         </is>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>0537880353</t>
+          <t>0570597742</t>
         </is>
       </c>
     </row>
     <row r="24" spans="1:6" customHeight="0">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t>Sheik Abdul Kader</t>
+          <t>Mohamed</t>
         </is>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>Vanathodu</t>
+          <t>Samir</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>Al Dawaa Medical Service Company</t>
+          <t>Alhabib</t>
         </is>
       </c>
       <c r="D24" s="0" t="inlineStr">
         <is>
-          <t>Head of international Brands commercial agreements</t>
+          <t>Pharmcistr</t>
         </is>
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
-          <t>sheik@al-dawaa.com.sa</t>
+          <t>mohamedsamir3361@gmiail.com</t>
         </is>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>0568287212</t>
+          <t>0540493958</t>
         </is>
       </c>
     </row>
     <row r="25" spans="1:6" customHeight="0">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t>Nadya</t>
+          <t>Ahmed</t>
         </is>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>Alfaraidy</t>
+          <t>Sami</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>King Fahd specialist Dammam </t>
+          <t>Dr hijazy medical center</t>
         </is>
       </c>
       <c r="D25" s="0" t="inlineStr">
         <is>
-          <t>Dermatology</t>
+          <t>Derma</t>
         </is>
       </c>
       <c r="E25" s="0" t="inlineStr">
         <is>
-          <t>nadya.alfaraidy@gmail.com</t>
+          <t>dr.ahmedsami2010@yahoo.com</t>
         </is>
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>0503831482</t>
+          <t>0531832638</t>
         </is>
       </c>
     </row>
     <row r="26" spans="1:6" customHeight="0">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t>Khalid</t>
+          <t>Nabila</t>
         </is>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>Al Wakeel</t>
+          <t>Ali</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>Al Dawaa Medical Services company</t>
+          <t>Smc</t>
         </is>
       </c>
       <c r="D26" s="0" t="inlineStr">
         <is>
-          <t>DMSCO International brands manager</t>
+          <t>Dermatologist </t>
         </is>
       </c>
       <c r="E26" s="0" t="inlineStr">
         <is>
-          <t>khalid.wakeel@al-dawaa.com.sa</t>
+          <t>nabiladr@hotmail.com</t>
         </is>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>0545045004</t>
+          <t>0500964161</t>
         </is>
       </c>
     </row>
     <row r="27" spans="1:6" customHeight="0">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t>Hosam</t>
+          <t>Salma</t>
         </is>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>Abdelmagid</t>
+          <t>Eid</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>Procare hospital</t>
+          <t>El nozha hospital</t>
         </is>
       </c>
       <c r="D27" s="0" t="inlineStr">
         <is>
-          <t>Dermatologist </t>
+          <t>Ophthalmology</t>
         </is>
       </c>
       <c r="E27" s="0" t="inlineStr">
         <is>
-          <t>hosamandroworld@hotmail.com</t>
+          <t>salmaeid19@gmail.com</t>
         </is>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>0556494406</t>
+          <t>0531832638</t>
         </is>
       </c>
     </row>
     <row r="28" spans="1:6" customHeight="0">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t>Mostafa</t>
+          <t>Kenana</t>
         </is>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>Sherif</t>
+          <t>Ghassan</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>Almana</t>
+          <t>New you clinic</t>
         </is>
       </c>
       <c r="D28" s="0" t="inlineStr">
         <is>
-          <t>Pediatrician </t>
+          <t>Dermatologist</t>
         </is>
       </c>
       <c r="E28" s="0" t="inlineStr">
         <is>
-          <t>mostafasherif74@yahoo.com</t>
+          <t>doctor_dermatologist@hotmail.com</t>
         </is>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>0549604588</t>
+          <t>0554382922</t>
         </is>
       </c>
     </row>
     <row r="29" spans="1:6" customHeight="0">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t>Mostafa</t>
+          <t>Noha</t>
         </is>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>Elhanoun</t>
+          <t>Ali</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t>STADA</t>
+          <t>Dr Suliman alhabib</t>
         </is>
       </c>
       <c r="D29" s="0" t="inlineStr">
         <is>
-          <t>Pharmacist </t>
+          <t>Dermatology</t>
         </is>
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
-          <t>mostafa.elhanoun@stada.com</t>
+          <t>alinuha26@gmail.com</t>
         </is>
       </c>
       <c r="F29" s="0" t="inlineStr">
         <is>
-          <t>0564095010</t>
+          <t>0567247475</t>
         </is>
       </c>
     </row>
     <row r="30" spans="1:6" customHeight="0">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t>Abdallah</t>
+          <t>Eslam</t>
         </is>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>Elshikh</t>
+          <t>Ghazal</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
-          <t>Aldawaa</t>
+          <t>M.o.h</t>
         </is>
       </c>
       <c r="D30" s="0" t="inlineStr">
         <is>
-          <t>Pharmacist </t>
+          <t>Derma</t>
         </is>
       </c>
       <c r="E30" s="0" t="inlineStr">
         <is>
-          <t>elshikhabdallah94@gmail.com</t>
+          <t>islamghazal@gmail.com</t>
         </is>
       </c>
       <c r="F30" s="0" t="inlineStr">
         <is>
-          <t>0541033263</t>
+          <t>0557818218</t>
         </is>
       </c>
     </row>
     <row r="31" spans="1:6" customHeight="0">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t>Hussein </t>
+          <t>Shaza </t>
         </is>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>Ahmed </t>
+          <t>Khalid</t>
         </is>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
-          <t>Al Dawaa </t>
+          <t>Qartier  clinc</t>
         </is>
       </c>
       <c r="D31" s="0" t="inlineStr">
         <is>
-          <t>Pharmacist </t>
+          <t>Dermatology</t>
         </is>
       </c>
       <c r="E31" s="0" t="inlineStr">
         <is>
-          <t>hussein.ahmed918@yahoo.com</t>
+          <t>shazakhalid25@hotmail.com</t>
         </is>
       </c>
       <c r="F31" s="0" t="inlineStr">
         <is>
-          <t>0501658132</t>
+          <t>0533092928</t>
         </is>
       </c>
     </row>
     <row r="32" spans="1:6" customHeight="0">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t>Nayera</t>
+          <t>Emadeldin </t>
         </is>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>Dakadosi</t>
+          <t>Ghozy</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t>Rawda</t>
+          <t>Military hospital</t>
         </is>
       </c>
       <c r="D32" s="0" t="inlineStr">
         <is>
-          <t>Dermatologist </t>
+          <t>F m</t>
         </is>
       </c>
       <c r="E32" s="0" t="inlineStr">
         <is>
-          <t>nayera.abdelkader@gmail.com</t>
+          <t>emadghozy@yahoo.com</t>
         </is>
       </c>
       <c r="F32" s="0" t="inlineStr">
         <is>
-          <t>0531998930</t>
+          <t>0534043332</t>
         </is>
       </c>
     </row>
     <row r="33" spans="1:6" customHeight="0">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t>Mohamed</t>
+          <t>Asmaa</t>
         </is>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>Elshamy</t>
+          <t>Agag</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>Alrai medical complex</t>
+          <t>A clinic</t>
         </is>
       </c>
       <c r="D33" s="0" t="inlineStr">
         <is>
-          <t>Pharmacist</t>
+          <t>Dermatologist</t>
         </is>
       </c>
       <c r="E33" s="0" t="inlineStr">
         <is>
-          <t>shamypharm@gmail.com</t>
+          <t>drsama14041984@gmail.com</t>
         </is>
       </c>
       <c r="F33" s="0" t="inlineStr">
         <is>
-          <t>0500658910</t>
+          <t>0541472673</t>
         </is>
       </c>
     </row>
     <row r="34" spans="1:6" customHeight="0">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t>Dr randa </t>
+          <t>M.fahed</t>
         </is>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>Yanni</t>
+          <t>g. Aswad</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
-          <t>Al Jazira clinic</t>
+          <t>Kh&amp;cc</t>
         </is>
       </c>
       <c r="D34" s="0" t="inlineStr">
         <is>
-          <t>Dermatologist</t>
+          <t>Dermatologist </t>
         </is>
       </c>
       <c r="E34" s="0" t="inlineStr">
         <is>
-          <t>randa.yani@yahoo.com</t>
+          <t>M.fahedhedg.aswed@gmail.com</t>
         </is>
       </c>
       <c r="F34" s="0" t="inlineStr">
         <is>
-          <t>559854179</t>
+          <t>0502469947</t>
         </is>
       </c>
     </row>
     <row r="35" spans="1:6" customHeight="0">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>Mona</t>
         </is>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>Fayyad</t>
+          <t>Hekal</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
         <is>
-          <t>Aldawaa</t>
+          <t>Aster Sanad hospital</t>
         </is>
       </c>
       <c r="D35" s="0" t="inlineStr">
         <is>
-          <t>Pharmacist </t>
+          <t>Registered dermatologist</t>
         </is>
       </c>
       <c r="E35" s="0" t="inlineStr">
         <is>
-          <t>doctorahmed990@gmail.com</t>
+          <t>monahekal815@yahoo.com</t>
         </is>
       </c>
       <c r="F35" s="0" t="inlineStr">
         <is>
-          <t>0540222156</t>
+          <t>0547389505</t>
         </is>
       </c>
     </row>
     <row r="36" spans="1:6" customHeight="0">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t>Mohamed</t>
+          <t>Nasser</t>
         </is>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>Mohamed</t>
+          <t>Saker</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
-          <t>Pharmacy</t>
+          <t>Altaawin alkharj</t>
         </is>
       </c>
       <c r="D36" s="0" t="inlineStr">
         <is>
-          <t>Pharmacist</t>
+          <t>Dermatology </t>
         </is>
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
-          <t>mohamed@gmail.com</t>
+          <t>nassersaker@yahoo.com</t>
         </is>
       </c>
       <c r="F36" s="0" t="inlineStr">
         <is>
-          <t>O562970203</t>
+          <t>0502223146</t>
         </is>
       </c>
     </row>
     <row r="37" spans="1:6" customHeight="0">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t>Amro</t>
+          <t>Sulaf</t>
         </is>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>Younes</t>
+          <t>Abdalla</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>AlDawa </t>
+          <t>Dalla</t>
         </is>
       </c>
       <c r="D37" s="0" t="inlineStr">
         <is>
-          <t>Pharmacist</t>
+          <t>Dermatology</t>
         </is>
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
-          <t>dr.amr.younes10@gmail.com</t>
+          <t>solafaabdalla29@gmail.com</t>
         </is>
       </c>
       <c r="F37" s="0" t="inlineStr">
         <is>
-          <t>0540914766</t>
+          <t>0567650876</t>
         </is>
       </c>
     </row>
     <row r="38" spans="1:6" customHeight="0">
       <c r="A38" s="0" t="inlineStr">
         <is>
-          <t>Taher</t>
+          <t>Marwa</t>
         </is>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>Abdelwahab</t>
+          <t>Elshowel</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>Aldawaa</t>
+          <t>Meras clinic</t>
         </is>
       </c>
       <c r="D38" s="0" t="inlineStr">
         <is>
-          <t>Pharmacist</t>
+          <t>Dermatologist </t>
         </is>
       </c>
       <c r="E38" s="0" t="inlineStr">
         <is>
-          <t>dr.taherayoub@gmail.com</t>
+          <t>marwawalid2013@gmail.com</t>
         </is>
       </c>
       <c r="F38" s="0" t="inlineStr">
         <is>
-          <t>0569848710</t>
+          <t>0566315908</t>
         </is>
       </c>
     </row>
     <row r="39" spans="1:6" customHeight="0">
       <c r="A39" s="0" t="inlineStr">
         <is>
-          <t>Rasha</t>
+          <t>Mervat</t>
         </is>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>Elsalakawy</t>
+          <t>Gabra</t>
         </is>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
-          <t>Hosn clinic</t>
+          <t>Prince Sattam Ben Abd alaziz university hospital </t>
         </is>
       </c>
       <c r="D39" s="0" t="inlineStr">
         <is>
-          <t>Dermatologist </t>
+          <t>Physcian</t>
         </is>
       </c>
       <c r="E39" s="0" t="inlineStr">
         <is>
-          <t>dr.rashaatef@gmail.com</t>
+          <t>dr.mgabra@gmail.com</t>
         </is>
       </c>
       <c r="F39" s="0" t="inlineStr">
         <is>
-          <t>0563040680</t>
+          <t>0509253216</t>
         </is>
       </c>
     </row>
     <row r="40" spans="1:6" customHeight="0">
       <c r="A40" s="0" t="inlineStr">
         <is>
-          <t>Salwa</t>
+          <t>Ahmed</t>
         </is>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>Biro</t>
+          <t>Alrumih</t>
         </is>
       </c>
       <c r="C40" s="0" t="inlineStr">
         <is>
-          <t>Mouwasat </t>
+          <t>Alhabib hospital </t>
         </is>
       </c>
       <c r="D40" s="0" t="inlineStr">
         <is>
-          <t>Derma</t>
+          <t>Dermatology </t>
         </is>
       </c>
       <c r="E40" s="0" t="inlineStr">
         <is>
-          <t>dr_kabotsha@yahoo.com</t>
+          <t>ahmedalrumih@gmail.com</t>
         </is>
       </c>
       <c r="F40" s="0" t="inlineStr">
         <is>
-          <t>0538626875</t>
+          <t>0504130208</t>
         </is>
       </c>
     </row>
     <row r="41" spans="1:6" customHeight="0">
       <c r="A41" s="0" t="inlineStr">
         <is>
-          <t>Amany</t>
+          <t>Ghada</t>
         </is>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>Gabra</t>
         </is>
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
-          <t>Alhijin</t>
+          <t>Suttam hospital university </t>
         </is>
       </c>
       <c r="D41" s="0" t="inlineStr">
         <is>
-          <t>Dermatology </t>
+          <t>Physicaln</t>
         </is>
       </c>
       <c r="E41" s="0" t="inlineStr">
         <is>
-          <t>amany.maher83@gmail.com</t>
+          <t>ghada.gabra@yahoo.com</t>
         </is>
       </c>
       <c r="F41" s="0" t="inlineStr">
         <is>
-          <t>0567349664</t>
+          <t>0557967138</t>
         </is>
       </c>
     </row>
     <row r="42" spans="1:6" customHeight="0">
       <c r="A42" s="0" t="inlineStr">
         <is>
-          <t>Mohamed </t>
+          <t>Islam</t>
         </is>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>Elgebaly</t>
+          <t>Rashad</t>
         </is>
       </c>
       <c r="C42" s="0" t="inlineStr">
         <is>
-          <t>Aldawaa</t>
+          <t>Cidic</t>
         </is>
       </c>
       <c r="D42" s="0" t="inlineStr">
         <is>
-          <t>Pharmacists </t>
+          <t>Dermatology </t>
         </is>
       </c>
       <c r="E42" s="0" t="inlineStr">
         <is>
-          <t>mgbaly1612@gmail.com</t>
+          <t>islamrashadabdou@gmail.com</t>
         </is>
       </c>
       <c r="F42" s="0" t="inlineStr">
         <is>
-          <t>0558294327</t>
+          <t>0501105564</t>
         </is>
       </c>
     </row>
     <row r="43" spans="1:6" customHeight="0">
       <c r="A43" s="0" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>Noura</t>
         </is>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>Rezk</t>
+          <t>Alsubei</t>
         </is>
       </c>
       <c r="C43" s="0" t="inlineStr">
         <is>
-          <t>Anak medical complex</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D43" s="0" t="inlineStr">
         <is>
-          <t>Dermatology </t>
+          <t>Neuro</t>
         </is>
       </c>
       <c r="E43" s="0" t="inlineStr">
         <is>
-          <t>rezk5@hotmail.com</t>
+          <t>loveamo2008@hotmail.com</t>
         </is>
       </c>
       <c r="F43" s="0" t="inlineStr">
         <is>
-          <t>0503819350</t>
+          <t>0536400522</t>
         </is>
       </c>
     </row>
     <row r="44" spans="1:6" customHeight="0">
       <c r="A44" s="0" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t>Abid</t>
+          <t>Alwaznah</t>
         </is>
       </c>
       <c r="C44" s="0" t="inlineStr">
         <is>
-          <t>Sulaiman Al Habib Khobar </t>
+          <t>Stada</t>
         </is>
       </c>
       <c r="D44" s="0" t="inlineStr">
         <is>
-          <t>Dermatology specialist</t>
+          <t>Activation manager</t>
         </is>
       </c>
       <c r="E44" s="0" t="inlineStr">
         <is>
-          <t>dr.mariaabid14@gmail.com</t>
+          <t>nda.z.w@hotmail.com</t>
         </is>
       </c>
       <c r="F44" s="0" t="inlineStr">
         <is>
-          <t>0500121982</t>
+          <t>0564958620</t>
         </is>
       </c>
     </row>
     <row r="45" spans="1:6" customHeight="0">
       <c r="A45" s="0" t="inlineStr">
         <is>
-          <t>Eslam</t>
+          <t>Manal </t>
         </is>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>Rakha</t>
+          <t>Tageldin</t>
         </is>
       </c>
       <c r="C45" s="0" t="inlineStr">
         <is>
-          <t>Aldawaa</t>
+          <t>Star smile</t>
         </is>
       </c>
       <c r="D45" s="0" t="inlineStr">
         <is>
-          <t>Pharmacist</t>
+          <t>Dermatologist</t>
         </is>
       </c>
       <c r="E45" s="0" t="inlineStr">
         <is>
-          <t>eslamrakha@gmail.com</t>
+          <t>ma_mo1984@yahoo.com</t>
         </is>
       </c>
       <c r="F45" s="0" t="inlineStr">
         <is>
-          <t>0566030693</t>
+          <t>0530758367</t>
         </is>
       </c>
     </row>
     <row r="46" spans="1:6" customHeight="0">
       <c r="A46" s="0" t="inlineStr">
         <is>
-          <t>Amr</t>
+          <t>Abobakr</t>
         </is>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t>Ali</t>
+          <t>Mohamed</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
         <is>
-          <t>Aldawaa</t>
+          <t>Stada</t>
         </is>
       </c>
       <c r="D46" s="0" t="inlineStr">
@@ -1525,221 +1525,221 @@
       </c>
       <c r="E46" s="0" t="inlineStr">
         <is>
-          <t>amrragab637@gmail.com</t>
+          <t>abobakr.nabil@stada.com</t>
         </is>
       </c>
       <c r="F46" s="0" t="inlineStr">
         <is>
-          <t>0553890218</t>
+          <t>0548916626</t>
         </is>
       </c>
     </row>
     <row r="47" spans="1:6" customHeight="0">
       <c r="A47" s="0" t="inlineStr">
         <is>
-          <t>Reda</t>
+          <t>Ahmed </t>
         </is>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t>Attia</t>
+          <t>Mandour</t>
         </is>
       </c>
       <c r="C47" s="0" t="inlineStr">
         <is>
-          <t>Aldawa</t>
+          <t>Hmg</t>
         </is>
       </c>
       <c r="D47" s="0" t="inlineStr">
         <is>
-          <t>Pharmacist</t>
+          <t>Pharmacist </t>
         </is>
       </c>
       <c r="E47" s="0" t="inlineStr">
         <is>
-          <t>redaelsabbag@gmail.com</t>
+          <t>ahmedragheb229@gmail.com</t>
         </is>
       </c>
       <c r="F47" s="0" t="inlineStr">
         <is>
-          <t>0547096651</t>
+          <t>0501104289</t>
         </is>
       </c>
     </row>
     <row r="48" spans="1:6" customHeight="0">
       <c r="A48" s="0" t="inlineStr">
         <is>
-          <t>Dr marina</t>
+          <t>Ahmed</t>
         </is>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>Naddaf</t>
+          <t>Shaban</t>
         </is>
       </c>
       <c r="C48" s="0" t="inlineStr">
         <is>
-          <t>Bright clinics</t>
+          <t>HMG</t>
         </is>
       </c>
       <c r="D48" s="0" t="inlineStr">
         <is>
-          <t>Dermatologist </t>
+          <t>Pharmacist</t>
         </is>
       </c>
       <c r="E48" s="0" t="inlineStr">
         <is>
-          <t>drmnaddaf@yahoo.com</t>
+          <t>ahmedshaaban055@gmail.com</t>
         </is>
       </c>
       <c r="F48" s="0" t="inlineStr">
         <is>
-          <t>0504853150</t>
+          <t>0562186467</t>
         </is>
       </c>
     </row>
     <row r="49" spans="1:6" customHeight="0">
       <c r="A49" s="0" t="inlineStr">
         <is>
-          <t>Magdy</t>
+          <t>Mohammed </t>
         </is>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>Mohamed</t>
+          <t>Tolan</t>
         </is>
       </c>
       <c r="C49" s="0" t="inlineStr">
         <is>
-          <t>Alwajdamedical</t>
+          <t>Hmg</t>
         </is>
       </c>
       <c r="D49" s="0" t="inlineStr">
         <is>
-          <t>Dermatologist </t>
+          <t>Pharmacist </t>
         </is>
       </c>
       <c r="E49" s="0" t="inlineStr">
         <is>
-          <t>magdy_alshimy@yahoo.com</t>
+          <t>mohamedtolan248@gmail.com</t>
         </is>
       </c>
       <c r="F49" s="0" t="inlineStr">
         <is>
-          <t>0505899062</t>
+          <t>0546402966</t>
         </is>
       </c>
     </row>
     <row r="50" spans="1:6" customHeight="0">
       <c r="A50" s="0" t="inlineStr">
         <is>
-          <t>Abdallah said</t>
+          <t>Dina</t>
         </is>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t>Mohamed</t>
+          <t>Elghetany</t>
         </is>
       </c>
       <c r="C50" s="0" t="inlineStr">
         <is>
-          <t>Dawaa</t>
+          <t>Stars smile</t>
         </is>
       </c>
       <c r="D50" s="0" t="inlineStr">
         <is>
-          <t>Pharmacist</t>
+          <t>Derma</t>
         </is>
       </c>
       <c r="E50" s="0" t="inlineStr">
         <is>
-          <t>dr.sheieif@gmail.com</t>
+          <t>dinamelghetany@gmail.com</t>
         </is>
       </c>
       <c r="F50" s="0" t="inlineStr">
         <is>
-          <t>0543962992</t>
+          <t>0599578582</t>
         </is>
       </c>
     </row>
     <row r="51" spans="1:6" customHeight="0">
       <c r="A51" s="0" t="inlineStr">
         <is>
-          <t>Mohamed</t>
+          <t>Hossam</t>
         </is>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t>Gamal</t>
+          <t>Shaban</t>
         </is>
       </c>
       <c r="C51" s="0" t="inlineStr">
         <is>
-          <t>Dawaa pharmacy</t>
+          <t>Hmg</t>
         </is>
       </c>
       <c r="D51" s="0" t="inlineStr">
         <is>
-          <t>Phst</t>
+          <t>Ph</t>
         </is>
       </c>
       <c r="E51" s="0" t="inlineStr">
         <is>
-          <t>ch.mohamed.gamal@gmail.com</t>
+          <t>hossamalrawda08@gmail.com</t>
         </is>
       </c>
       <c r="F51" s="0" t="inlineStr">
         <is>
-          <t>569486212</t>
+          <t>0548903773</t>
         </is>
       </c>
     </row>
     <row r="52" spans="1:6" customHeight="0">
       <c r="A52" s="0" t="inlineStr">
         <is>
-          <t>Islam</t>
+          <t>Misk</t>
         </is>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t>Elsayed</t>
+          <t>Alshreef</t>
         </is>
       </c>
       <c r="C52" s="0" t="inlineStr">
         <is>
-          <t>Aldawaa</t>
+          <t>Mooler</t>
         </is>
       </c>
       <c r="D52" s="0" t="inlineStr">
         <is>
-          <t>Pharmacist </t>
+          <t>Moler</t>
         </is>
       </c>
       <c r="E52" s="0" t="inlineStr">
         <is>
-          <t>dr.shereif@gmail.com</t>
+          <t>e1415ee@gmail.c0m</t>
         </is>
       </c>
       <c r="F52" s="0" t="inlineStr">
         <is>
-          <t>0507760002</t>
+          <t>0567677373</t>
         </is>
       </c>
     </row>
     <row r="53" spans="1:6" customHeight="0">
       <c r="A53" s="0" t="inlineStr">
         <is>
-          <t>Shaymaa</t>
+          <t>Mohammad</t>
         </is>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t>Abdelmaksoud</t>
+          <t>Alrifai</t>
         </is>
       </c>
       <c r="C53" s="0" t="inlineStr">
         <is>
-          <t>Almana hospital</t>
+          <t>HMC - Alnarjas</t>
         </is>
       </c>
       <c r="D53" s="0" t="inlineStr">
@@ -1749,300 +1749,172 @@
       </c>
       <c r="E53" s="0" t="inlineStr">
         <is>
-          <t>omaralmokhtar75511@yahoo.com</t>
+          <t>dr.mhmdrifai@gmail.com</t>
         </is>
       </c>
       <c r="F53" s="0" t="inlineStr">
         <is>
-          <t>0560897133</t>
+          <t>0582881888</t>
         </is>
       </c>
     </row>
     <row r="54" spans="1:6" customHeight="0">
       <c r="A54" s="0" t="inlineStr">
         <is>
-          <t>Eman</t>
+          <t>Oumayma</t>
         </is>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>Elsharkawy</t>
+          <t>Mani</t>
         </is>
       </c>
       <c r="C54" s="0" t="inlineStr">
         <is>
-          <t>Royal</t>
+          <t>Habit center narjiss</t>
         </is>
       </c>
       <c r="D54" s="0" t="inlineStr">
         <is>
-          <t>Dermatologist </t>
+          <t>Dermatology </t>
         </is>
       </c>
       <c r="E54" s="0" t="inlineStr">
         <is>
-          <t>dr.mino-06@yahoo.com</t>
+          <t>oumaymamani3@gmail.com</t>
         </is>
       </c>
       <c r="F54" s="0" t="inlineStr">
         <is>
-          <t>054760238</t>
+          <t>0534064074</t>
         </is>
       </c>
     </row>
     <row r="55" spans="1:6" customHeight="0">
       <c r="A55" s="0" t="inlineStr">
         <is>
-          <t>Amira Gouda Issa </t>
+          <t>Izzedeen</t>
         </is>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>Moustafa</t>
+          <t>Almomani</t>
         </is>
       </c>
       <c r="C55" s="0" t="inlineStr">
         <is>
-          <t>Al mana general hospital</t>
+          <t>HMG narjes</t>
         </is>
       </c>
       <c r="D55" s="0" t="inlineStr">
         <is>
-          <t>Dermatologist </t>
+          <t>Dermatology </t>
         </is>
       </c>
       <c r="E55" s="0" t="inlineStr">
         <is>
-          <t>amiragooda2018@gmail.com</t>
+          <t>azodeen@gmail.com</t>
         </is>
       </c>
       <c r="F55" s="0" t="inlineStr">
         <is>
-          <t>0506697532</t>
+          <t>0510198386</t>
         </is>
       </c>
     </row>
     <row r="56" spans="1:6" customHeight="0">
       <c r="A56" s="0" t="inlineStr">
         <is>
-          <t>Asmaa</t>
+          <t>Diana gamal</t>
         </is>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>Rashawn </t>
+          <t>Foad</t>
         </is>
       </c>
       <c r="C56" s="0" t="inlineStr">
         <is>
-          <t>Alvdossary hospital </t>
+          <t>Ok clinic</t>
         </is>
       </c>
       <c r="D56" s="0" t="inlineStr">
         <is>
-          <t>Pediatrics </t>
+          <t>Dermatology</t>
         </is>
       </c>
       <c r="E56" s="0" t="inlineStr">
         <is>
-          <t>dr.asmaarashwanx2@gmail.com</t>
+          <t>drdayanagamal@gmail.com</t>
         </is>
       </c>
       <c r="F56" s="0" t="inlineStr">
         <is>
-          <t>0504895529</t>
+          <t>0557113627</t>
         </is>
       </c>
     </row>
     <row r="57" spans="1:6" customHeight="0">
       <c r="A57" s="0" t="inlineStr">
         <is>
-          <t>Hussein elmorsy</t>
+          <t>Dr Syed</t>
         </is>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>Ibrahim</t>
+          <t>Khizar</t>
         </is>
       </c>
       <c r="C57" s="0" t="inlineStr">
         <is>
-          <t>Dawaa</t>
+          <t>Sulaiman Al Habib</t>
         </is>
       </c>
       <c r="D57" s="0" t="inlineStr">
         <is>
-          <t>Pharmacist </t>
+          <t>Dermatology </t>
         </is>
       </c>
       <c r="E57" s="0" t="inlineStr">
         <is>
-          <t>hussienelmorsy60@gmail.com</t>
+          <t>drsyedkhizar@hotmail.com</t>
         </is>
       </c>
       <c r="F57" s="0" t="inlineStr">
         <is>
-          <t>0533986019</t>
+          <t>0530039395</t>
         </is>
       </c>
     </row>
     <row r="58" spans="1:6" customHeight="0">
       <c r="A58" s="0" t="inlineStr">
         <is>
-          <t>Ehab</t>
+          <t>Ali</t>
         </is>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>Elhatim</t>
+          <t>Mahmoud</t>
         </is>
       </c>
       <c r="C58" s="0" t="inlineStr">
         <is>
-          <t>Almana g hospital</t>
+          <t>Hamadi</t>
         </is>
       </c>
       <c r="D58" s="0" t="inlineStr">
         <is>
-          <t>Dermatologist </t>
+          <t>Derma</t>
         </is>
       </c>
       <c r="E58" s="0" t="inlineStr">
         <is>
-          <t>ehab.ilhateem@yahoo.com</t>
+          <t>alihm600700@hotmail.com</t>
         </is>
       </c>
       <c r="F58" s="0" t="inlineStr">
         <is>
-          <t>0590208955</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" spans="1:6" customHeight="0">
-      <c r="A59" s="0" t="inlineStr">
-        <is>
-          <t>Mohamed </t>
-        </is>
-      </c>
-      <c r="B59" s="0" t="inlineStr">
-        <is>
-          <t>Kafafy</t>
-        </is>
-      </c>
-      <c r="C59" s="0" t="inlineStr">
-        <is>
-          <t>Alhokil</t>
-        </is>
-      </c>
-      <c r="D59" s="0" t="inlineStr">
-        <is>
-          <t>Dermatologist </t>
-        </is>
-      </c>
-      <c r="E59" s="0" t="inlineStr">
-        <is>
-          <t>dermaland2007@yahoo.com</t>
-        </is>
-      </c>
-      <c r="F59" s="0" t="inlineStr">
-        <is>
-          <t>0565994357</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" spans="1:6" customHeight="0">
-      <c r="A60" s="0" t="inlineStr">
-        <is>
-          <t>Nabia</t>
-        </is>
-      </c>
-      <c r="B60" s="0" t="inlineStr">
-        <is>
-          <t>Dawood</t>
-        </is>
-      </c>
-      <c r="C60" s="0" t="inlineStr">
-        <is>
-          <t>Sulaiman Al habib khobar</t>
-        </is>
-      </c>
-      <c r="D60" s="0" t="inlineStr">
-        <is>
-          <t>Dermatology</t>
-        </is>
-      </c>
-      <c r="E60" s="0" t="inlineStr">
-        <is>
-          <t>nab.bia@gmail.com</t>
-        </is>
-      </c>
-      <c r="F60" s="0" t="inlineStr">
-        <is>
-          <t>0580021128</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" spans="1:6" customHeight="0">
-      <c r="A61" s="0" t="inlineStr">
-        <is>
-          <t>Abdallah gamal</t>
-        </is>
-      </c>
-      <c r="B61" s="0" t="inlineStr">
-        <is>
-          <t>Farhan</t>
-        </is>
-      </c>
-      <c r="C61" s="0" t="inlineStr">
-        <is>
-          <t>Dawaa 789</t>
-        </is>
-      </c>
-      <c r="D61" s="0" t="inlineStr">
-        <is>
-          <t>Pharmacist</t>
-        </is>
-      </c>
-      <c r="E61" s="0" t="inlineStr">
-        <is>
-          <t>abdallahex19@gmail.com</t>
-        </is>
-      </c>
-      <c r="F61" s="0" t="inlineStr">
-        <is>
-          <t>0541626080</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" spans="1:6" customHeight="0">
-      <c r="A62" s="0" t="inlineStr">
-        <is>
-          <t>Ahmed</t>
-        </is>
-      </c>
-      <c r="B62" s="0" t="inlineStr">
-        <is>
-          <t>Saadoun</t>
-        </is>
-      </c>
-      <c r="C62" s="0" t="inlineStr">
-        <is>
-          <t>Dawaa pharmacy</t>
-        </is>
-      </c>
-      <c r="D62" s="0" t="inlineStr">
-        <is>
-          <t>Pharmacist</t>
-        </is>
-      </c>
-      <c r="E62" s="0" t="inlineStr">
-        <is>
-          <t>ahmedsaadoun974@gmail.com</t>
-        </is>
-      </c>
-      <c r="F62" s="0" t="inlineStr">
-        <is>
-          <t>0544835264</t>
+          <t>0549823271</t>
         </is>
       </c>
     </row>
